--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486309_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486309_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7488</v>
+        <v>2.4559</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2076</v>
+        <v>2.7605</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4588</v>
+        <v>-0.3046</v>
       </c>
       <c r="G2" t="n">
         <v>1.4197</v>
@@ -610,13 +610,13 @@
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2193</v>
+        <v>-0.0736</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6682</v>
+        <v>0.2211</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4488</v>
+        <v>-0.2947</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1952</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7208</v>
+        <v>1.6284</v>
       </c>
       <c r="E3" t="n">
-        <v>1.454</v>
+        <v>0.3616</v>
       </c>
       <c r="F3" t="n">
         <v>1.2668</v>
@@ -688,10 +688,10 @@
         <v>2.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9612</v>
+        <v>0.8688</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6788</v>
+        <v>0.5864</v>
       </c>
       <c r="U3" t="n">
         <v>0.2824</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.084</v>
+        <v>0.7441</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9762</v>
+        <v>2.8211</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8922</v>
+        <v>-2.0771</v>
       </c>
       <c r="G4" t="n">
         <v>0.0823</v>
@@ -766,13 +766,13 @@
         <v>0.6525</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2158</v>
+        <v>-0.5558</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1971</v>
+        <v>0.0421</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4129</v>
+        <v>-0.5979</v>
       </c>
       <c r="V4" t="n">
         <v>0.5649999999999999</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1043</v>
+        <v>0.5037</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0063</v>
+        <v>0.5218</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1105</v>
+        <v>-0.0181</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7226</v>
@@ -844,13 +844,13 @@
         <v>1.7401</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7519</v>
+        <v>-0.1439</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0769</v>
+        <v>0.4386</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.675</v>
+        <v>-0.5825</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3698</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2744</v>
+        <v>-1.3061</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2109</v>
+        <v>-0.3659</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0635</v>
+        <v>-0.9402</v>
       </c>
       <c r="G6" t="n">
         <v>-0.1789</v>
@@ -922,13 +922,13 @@
         <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0308</v>
+        <v>-0.0625</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6682</v>
+        <v>0.5131</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6989</v>
+        <v>-0.5756</v>
       </c>
       <c r="V6" t="n">
         <v>-1.4997</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2685</v>
+        <v>-1.7838</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3832</v>
+        <v>0.8988</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.6518</v>
+        <v>-2.6826</v>
       </c>
       <c r="G7" t="n">
         <v>-4.0456</v>
@@ -1000,13 +1000,13 @@
         <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2006</v>
+        <v>-0.7159</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1454</v>
+        <v>0.3701</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0552</v>
+        <v>-1.086</v>
       </c>
       <c r="V7" t="n">
         <v>1.8902</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7881</v>
+        <v>-2.3043</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5714</v>
+        <v>-2.2109</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2167</v>
+        <v>-0.0934</v>
       </c>
       <c r="G8" t="n">
         <v>-2.0808</v>
@@ -1078,13 +1078,13 @@
         <v>0.2175</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9248</v>
+        <v>-0.441</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.411</v>
+        <v>-0.0505</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5138</v>
+        <v>-0.3906</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.0895</v>
+        <v>-4.126</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.5472</v>
+        <v>-4.522</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4576</v>
+        <v>0.396</v>
       </c>
       <c r="G9" t="n">
         <v>-4.1975</v>
@@ -1156,13 +1156,13 @@
         <v>1.5225</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3271</v>
+        <v>-0.3635</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4194</v>
+        <v>-0.3941</v>
       </c>
       <c r="U9" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.0306</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8131</v>
+        <v>-4.2792</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5724</v>
+        <v>-3.1002</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2407</v>
+        <v>-1.1791</v>
       </c>
       <c r="G10" t="n">
         <v>-2.4693</v>
@@ -1234,13 +1234,13 @@
         <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1714</v>
+        <v>-0.6375</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9589</v>
+        <v>-0.4867</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2125</v>
+        <v>-0.1508</v>
       </c>
       <c r="V10" t="n">
         <v>-2.2599</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2107</v>
+        <v>-4.6451</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.8042</v>
+        <v>-4.1769</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4065</v>
+        <v>-0.4681</v>
       </c>
       <c r="G11" t="n">
         <v>-3.4175</v>
@@ -1312,13 +1312,13 @@
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2706</v>
+        <v>0.295</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3425</v>
+        <v>0.2848</v>
       </c>
       <c r="U11" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0102</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.3643</v>
+        <v>-6.2196</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.6602</v>
+        <v>-7.2997</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2959</v>
+        <v>1.0801</v>
       </c>
       <c r="G12" t="n">
         <v>-5.0796</v>
@@ -1390,13 +1390,13 @@
         <v>1.5225</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.08740000000000001</v>
+        <v>0.0574</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4194</v>
+        <v>-0.0589</v>
       </c>
       <c r="U12" t="n">
-        <v>0.332</v>
+        <v>0.1163</v>
       </c>
       <c r="V12" t="n">
         <v>0.7602</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-20.3593</v>
+        <v>-19.332</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.339</v>
+        <v>-14.3118</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.0204</v>
+        <v>-5.0203</v>
       </c>
       <c r="G13" t="n">
         <v>-19.6703</v>
@@ -1468,13 +1468,13 @@
         <v>14.1377</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.7999</v>
+        <v>-1.7725</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4388000000000003</v>
+        <v>1.466</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.2385</v>
+        <v>-3.238599999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-2.239199999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.8855</v>
+        <v>7.1533</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4128</v>
+        <v>2.7422</v>
       </c>
       <c r="F14" t="n">
-        <v>4.4727</v>
+        <v>4.4111</v>
       </c>
       <c r="G14" t="n">
         <v>5.6951</v>
@@ -1546,13 +1546,13 @@
         <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7554</v>
+        <v>1.0232</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4132</v>
+        <v>0.7427</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3422</v>
+        <v>0.2806</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.7114</v>
+        <v>5.3298</v>
       </c>
       <c r="E15" t="n">
-        <v>2.866</v>
+        <v>2.0837</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8454</v>
+        <v>3.2461</v>
       </c>
       <c r="G15" t="n">
         <v>3.0139</v>
@@ -1624,13 +1624,13 @@
         <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1973</v>
+        <v>0.8157</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7557</v>
+        <v>0.9734</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5584</v>
+        <v>-0.1577</v>
       </c>
       <c r="V15" t="n">
         <v>0.1952</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>S. CECCARDI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.887</v>
+        <v>4.5659</v>
       </c>
       <c r="E16" t="n">
-        <v>0.387</v>
+        <v>0.5593</v>
       </c>
       <c r="F16" t="n">
-        <v>4.5</v>
+        <v>4.0065</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3231</v>
+        <v>4.4436</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0888</v>
+        <v>1.3232</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2343</v>
+        <v>3.1205</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6236</v>
+        <v>1.4818</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.0698</v>
+        <v>0.4475</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5538</v>
+        <v>1.0343</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9467</v>
+        <v>2.9618</v>
       </c>
       <c r="N16" t="n">
-        <v>1.1586</v>
+        <v>0.8757</v>
       </c>
       <c r="O16" t="n">
-        <v>1.7881</v>
+        <v>2.0862</v>
       </c>
       <c r="P16" t="n">
-        <v>0.87</v>
+        <v>-0.435</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R16" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4541</v>
+        <v>0.1875</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0106</v>
+        <v>0.1226</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4435</v>
+        <v>0.0649</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7602</v>
+        <v>0.3698</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
         <v>-0.7602</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. GEU</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.6683</v>
+        <v>3.9969</v>
       </c>
       <c r="E17" t="n">
-        <v>3.5604</v>
+        <v>0.0517</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1079</v>
+        <v>3.9452</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2471</v>
+        <v>2.3231</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6088</v>
+        <v>1.0888</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6383</v>
+        <v>1.2343</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6767</v>
+        <v>-0.6236</v>
       </c>
       <c r="K17" t="n">
-        <v>1.083</v>
+        <v>-0.0698</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5937</v>
+        <v>-0.5538</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5704</v>
+        <v>2.9467</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5258</v>
+        <v>1.1586</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0446</v>
+        <v>1.7881</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.435</v>
+        <v>0.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3565</v>
+        <v>1.564</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2762</v>
+        <v>0.6754</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0803</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4997</v>
+        <v>-0.7602</v>
       </c>
       <c r="W17" t="n">
-        <v>1.695</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1952</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. CECCARDI</t>
+          <t>D. GEU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.772</v>
+        <v>3.6008</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1112</v>
+        <v>2.5545</v>
       </c>
       <c r="F18" t="n">
-        <v>3.8832</v>
+        <v>1.0463</v>
       </c>
       <c r="G18" t="n">
-        <v>4.4436</v>
+        <v>2.2471</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3232</v>
+        <v>1.6088</v>
       </c>
       <c r="I18" t="n">
-        <v>3.1205</v>
+        <v>0.6383</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4818</v>
+        <v>1.6767</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4475</v>
+        <v>1.083</v>
       </c>
       <c r="L18" t="n">
-        <v>1.0343</v>
+        <v>0.5937</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9618</v>
+        <v>0.5704</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8757</v>
+        <v>0.5258</v>
       </c>
       <c r="O18" t="n">
-        <v>2.0862</v>
+        <v>0.0446</v>
       </c>
       <c r="P18" t="n">
         <v>-0.435</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7401</v>
+        <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6064000000000001</v>
+        <v>0.289</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.548</v>
+        <v>0.2704</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0584</v>
+        <v>0.0186</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3698</v>
+        <v>1.4997</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.695</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.7602</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.9669</v>
+        <v>2.9843</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4375</v>
+        <v>3.3315</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4705</v>
+        <v>-0.3472</v>
       </c>
       <c r="G19" t="n">
         <v>5.4998</v>
@@ -1936,13 +1936,13 @@
         <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0979</v>
+        <v>-0.0805</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.548</v>
+        <v>0.3461</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5499000000000001</v>
+        <v>-0.4266</v>
       </c>
       <c r="V19" t="n">
         <v>-1.13</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1729</v>
+        <v>1.5621</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8177</v>
+        <v>1.9295</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6448</v>
+        <v>-0.3674</v>
       </c>
       <c r="G20" t="n">
         <v>1.3184</v>
@@ -2014,13 +2014,13 @@
         <v>0.2175</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.363</v>
+        <v>0.0261</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0601</v>
+        <v>0.1719</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4231</v>
+        <v>-0.1457</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3884</v>
+        <v>0.3961</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0363</v>
+        <v>0.1872</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4247</v>
+        <v>0.2089</v>
       </c>
       <c r="G21" t="n">
         <v>0.2823</v>
@@ -2092,13 +2092,13 @@
         <v>0.2175</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1114</v>
+        <v>-0.1036</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2055</v>
+        <v>0.018</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0941</v>
+        <v>-0.1217</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.2613</v>
       </c>
       <c r="E22" t="n">
         <v>-1.3196</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3959</v>
+        <v>1.5808</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6512</v>
@@ -2170,13 +2170,13 @@
         <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2278</v>
+        <v>0.4128</v>
       </c>
       <c r="T22" t="n">
         <v>0.3257</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0978</v>
+        <v>0.0871</v>
       </c>
       <c r="V22" t="n">
         <v>1.4997</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.237</v>
+        <v>-1.9827</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6591</v>
+        <v>-1.4356</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5779</v>
+        <v>-0.5471</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7541</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.483</v>
+        <v>-0.2286</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2055</v>
+        <v>0.018</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2775</v>
+        <v>-0.2466</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8728</v>
+        <v>-2.3449</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5455</v>
+        <v>-0.9868</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3273</v>
+        <v>-1.3581</v>
       </c>
       <c r="G24" t="n">
         <v>-1.0007</v>
@@ -2326,13 +2326,13 @@
         <v>0.87</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1321</v>
+        <v>-0.6042</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.1947</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3787</v>
+        <v>-0.4095</v>
       </c>
       <c r="V24" t="n">
         <v>0.5649999999999999</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.0594</v>
+        <v>-5.1635</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.7892</v>
+        <v>-4.6774</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2703</v>
+        <v>-0.486</v>
       </c>
       <c r="G25" t="n">
         <v>-0.7469</v>
@@ -2404,13 +2404,13 @@
         <v>0.435</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3974</v>
+        <v>-0.5014</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3425</v>
+        <v>-0.2307</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0549</v>
+        <v>-0.2707</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>20.3595</v>
+        <v>20.3594</v>
       </c>
       <c r="E26" t="n">
-        <v>5.020499999999999</v>
+        <v>5.0202</v>
       </c>
       <c r="F26" t="n">
-        <v>15.339</v>
+        <v>15.3391</v>
       </c>
       <c r="G26" t="n">
         <v>19.6704</v>
@@ -2455,7 +2455,7 @@
         <v>16.6902</v>
       </c>
       <c r="J26" t="n">
-        <v>7.8146</v>
+        <v>7.814600000000002</v>
       </c>
       <c r="K26" t="n">
         <v>-0.1342</v>
@@ -2482,13 +2482,13 @@
         <v>9.787599999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>2.7999</v>
+        <v>2.8</v>
       </c>
       <c r="T26" t="n">
-        <v>3.2385</v>
+        <v>3.238799999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4385999999999999</v>
+        <v>-0.4387</v>
       </c>
       <c r="V26" t="n">
         <v>2.2392</v>
